--- a/human_validation/judge/kor/judge_D012_S004_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D012_S004_P003__gemini-3.8-flash_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,82 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 엘리베이터가 정말 무서워서 왔어요. 실제로 위험하지 않다는 건 아는데, 엘리베이터를 타야 할 때면 갇힐 것 같은 느낌이 들고, 아무리 애써도 괜찮다는 느낌이 안 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 특정공포증 (D012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이 강렬한 두려움이 엘리베이터에서만 나타나나요, 아니면 다른 상황에서도 경험하시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 정말 엘리베이터 때문이에요. 실제로 위험하지 않다는 건 아는데, 일단 타야 하면 갇힐 것 같아서 무서워지고, 아무리 애써도 괜찮다는 느낌이 안 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 특정공포증 (D012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 엘리베이터에 대한 이런 두려움을 얼마나 오래 겪고 계신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 지금 한 11개월 정도 됐어요. 집을 잃고 상층 아파트로 이사한 뒤부터 시작됐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 특정공포증 (D012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>진단명: 특정공포증 (D012)
 인구통계: 성별 여성 / 나이 34 / 직업상태 construction laborer / 최종학력 고등학교 중퇴
@@ -575,131 +642,32 @@
 증상 지속 기간: 11 months
 추가 요건: 
 주호소 증상 코드: S062
-배경 서술: 압류 절차로 인해 린다와 남편이 작은 집에서 쫓겨나 임대 아파트 상층으로 이사하게 되면서, 엘리베이터는 이전에는 전혀 그렇지 않았던 방식으로 그녀의 일상 일부가 되었다. 11개월에 걸쳐 그녀는 문이 닫히는 순간 즉각적으로 나타나는, 엘리베이터에 국한된 두려움을 갖게 되어 보통 계단을 이용했고, 권양기나 엘리베이터가 유일한 실질적인 접근 수단인 건물에서의 작업 배정을 피했다. 그녀는 여전히 일과 GED 수업을 계속할 수 있었지만, 우회로로 인해 지각하고 지쳤으며 특정 건설 작업에는 투입되기 어려워져 뚜렷한 기능적 지장이 나타났다. 린다는 매주 얼마나 많은 시간을 잃고 있는지 계산해본 뒤 지역사회 보건소 방문 때 이를 언급했고, 정신과 평가를 의뢰받았다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 엘리베이터가 정말 무서워서 왔어요. 실제로 위험하지 않다는 건 아는데, 엘리베이터를 타야 할 때면 갇힐 것 같은 느낌이 들고, 아무리 애써도 괜찮다는 느낌이 안 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이 강렬한 두려움이 엘리베이터에서만 나타나나요, 아니면 다른 상황에서도 경험하시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 정말 엘리베이터 때문이에요. 실제로 위험하지 않다는 건 아는데, 일단 타야 하면 갇힐 것 같아서 무서워지고, 아무리 애써도 괜찮다는 느낌이 안 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 엘리베이터에 대한 이런 두려움을 얼마나 오래 겪고 계신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 지금 한 11개월 정도 됐어요. 집을 잃고 상층 아파트로 이사한 뒤부터 시작됐어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
+배경 서술: 압류 절차로 인해 린다와 남편이 작은 집에서 쫓겨나 임대 아파트 상층으로 이사하게 되면서, 엘리베이터는 이전에는 전혀 그렇지 않았던 방식으로 그녀의 일상 일부가 되었다. 11개월에 걸쳐 그녀는 문이 닫히는 순간 즉각적으로 나타나는, 엘리베이터에 국한된 두려움을 갖게 되어 보통 계단을 이용했고, 권양기나 엘리베이터가 유일한 실질적인 접근 수단인 건물에서의 작업 배정을 피했다. 그녀는 여전히 일과 GED 수업을 계속할 수 있었지만, 우회로로 인해 지각하고 지쳤으며 특정 건설 작업에는 투입되기 어려워져 뚜렷한 기능적 지장이 나타났다. 린다는 매주 얼마나 많은 시간을 잃고 있는지 계산해본 뒤 지역사회 보건소 방문 때 이를 언급했고, 정신과 평가를 의뢰받았다.
+표집된 증상 목록:
+  - S062 특정 공포 대상에 대한 두려움: 실제 위험에 비해 지나치게 강한, 특정 대상이나 상황에 대한 뚜렷한 두려움이나 불안(아동의 경우 울음, 떼쓰기, 얼어붙음, 매달림으로 표현될 수 있음).
+  - S063 즉각적 공포/불안 반응: 공포 대상이나 상황에 노출되면 거의 항상 즉각적인 두려움이나 불안이 유발됨.
+  - S064 공포 대상 회피/견딤: 공포 대상이나 상황을 적극적으로 회피하거나 강한 두려움·불안을 견디며 버팀.</t>
+        </is>
+      </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 특정공포증 (D012)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 특정공포증 (D012, ICD: F40.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: phobic_symptoms (관계=must_include, 요구개수=3, 충족개수=2, 커버리지=0.6667)
-  확인된 근거: 특정 공포 대상에 대한 두려움: 실제 위험에 비해 지나치게 강한, 특정 대상이나 상황에 대한 뚜렷한 두려움이나 불안(아동의 경우 울음, 떼쓰기, 얼어붙음, 매달림으로 표현될 수 있음).; 즉각적 공포/불안 반응: 공포 대상이나 상황에 노출되면 거의 항상 즉각적인 두려움이나 불안이 유발됨.
-  누락: 공포 대상 회피/견딤: 공포 대상이나 상황을 적극적으로 회피하거나 강한 두려움·불안을 견디며 버팀.</t>
+          <t>의사의 최종 진단: 특정공포증 (D012, ICD: F40.2)
+지속 기간 요건: 있음
+기능적 손상 요건: 없음
+추가 요건: None
+체크리스트 그룹: phobic_symptoms (관계=must_include, 요구개수=3, 충족개수=2, 커버리지=0.6667)
+확인된 근거:
+  - 특정 공포 대상에 대한 두려움: 실제 위험에 비해 지나치게 강한, 특정 대상이나 상황에 대한 뚜렷한 두려움이나 불안(아동의 경우 울음, 떼쓰기, 얼어붙음, 매달림으로 표현될 수 있음).
+  - 즉각적 공포/불안 반응: 공포 대상이나 상황에 노출되면 거의 항상 즉각적인 두려움이나 불안이 유발됨.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D012_S004_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D012_S004_P003__gemini-3.8-flash_kor.xlsx
@@ -628,6 +628,11 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -663,11 +668,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D012_S004_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D012_S004_P003__gemini-3.8-flash_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -555,6 +556,7 @@
         <v>0.3333</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
